--- a/mapping-mechanisms/ig/cm-v3-administrative-gender.xlsx
+++ b/mapping-mechanisms/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T07:15:56+00:00</t>
+    <t>2026-04-07T12:56:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mapping-mechanisms/ig/cm-v3-administrative-gender.xlsx
+++ b/mapping-mechanisms/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T12:56:50+00:00</t>
+    <t>2026-04-08T07:34:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mapping-mechanisms/ig/cm-v3-administrative-gender.xlsx
+++ b/mapping-mechanisms/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T07:34:22+00:00</t>
+    <t>2026-04-08T12:03:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mapping-mechanisms/ig/cm-v3-administrative-gender.xlsx
+++ b/mapping-mechanisms/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T12:03:15+00:00</t>
+    <t>2026-04-08T12:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mapping-mechanisms/ig/cm-v3-administrative-gender.xlsx
+++ b/mapping-mechanisms/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T12:03:44+00:00</t>
+    <t>2026-04-08T12:06:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mapping-mechanisms/ig/cm-v3-administrative-gender.xlsx
+++ b/mapping-mechanisms/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T12:06:40+00:00</t>
+    <t>2026-04-08T12:09:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mapping-mechanisms/ig/cm-v3-administrative-gender.xlsx
+++ b/mapping-mechanisms/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T12:09:30+00:00</t>
+    <t>2026-04-08T12:10:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mapping-mechanisms/ig/cm-v3-administrative-gender.xlsx
+++ b/mapping-mechanisms/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T12:10:30+00:00</t>
+    <t>2026-04-08T12:26:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mapping-mechanisms/ig/cm-v3-administrative-gender.xlsx
+++ b/mapping-mechanisms/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T12:26:09+00:00</t>
+    <t>2026-04-08T13:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mapping-mechanisms/ig/cm-v3-administrative-gender.xlsx
+++ b/mapping-mechanisms/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:01:02+00:00</t>
+    <t>2026-04-09T10:02:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
